--- a/utils/planilhas_competidores/Arthur_previsoes.xlsx
+++ b/utils/planilhas_competidores/Arthur_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD07A3B-E0B4-4D1B-8ADF-793DC69ADD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9420CF67-C259-4034-AE95-1AECF4B8588D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -822,6 +822,12 @@
       <c r="G4" t="s">
         <v>21</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -845,6 +851,12 @@
       <c r="G5" t="s">
         <v>18</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -868,6 +880,12 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -891,6 +909,12 @@
       <c r="G7" t="s">
         <v>24</v>
       </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -972,6 +996,12 @@
       <c r="G10" t="s">
         <v>34</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -995,6 +1025,12 @@
       <c r="G11" t="s">
         <v>36</v>
       </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1018,6 +1054,12 @@
       <c r="G12" t="s">
         <v>36</v>
       </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1041,6 +1083,12 @@
       <c r="G13" t="s">
         <v>37</v>
       </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1122,6 +1170,12 @@
       <c r="G16" t="s">
         <v>44</v>
       </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1145,6 +1199,12 @@
       <c r="G17" t="s">
         <v>46</v>
       </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1168,6 +1228,12 @@
       <c r="G18" t="s">
         <v>21</v>
       </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1191,6 +1257,12 @@
       <c r="G19" t="s">
         <v>47</v>
       </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1272,6 +1344,12 @@
       <c r="G22" t="s">
         <v>37</v>
       </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1295,6 +1373,12 @@
       <c r="G23" t="s">
         <v>56</v>
       </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1318,6 +1402,12 @@
       <c r="G24" t="s">
         <v>34</v>
       </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -1341,6 +1431,12 @@
       <c r="G25" t="s">
         <v>56</v>
       </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1422,6 +1518,12 @@
       <c r="G28" t="s">
         <v>29</v>
       </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1445,6 +1547,12 @@
       <c r="G29" t="s">
         <v>68</v>
       </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1468,6 +1576,12 @@
       <c r="G30" t="s">
         <v>46</v>
       </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1491,6 +1605,12 @@
       <c r="G31" t="s">
         <v>41</v>
       </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1572,6 +1692,12 @@
       <c r="G34" t="s">
         <v>62</v>
       </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1595,6 +1721,12 @@
       <c r="G35" t="s">
         <v>24</v>
       </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1618,6 +1750,12 @@
       <c r="G36" t="s">
         <v>72</v>
       </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1641,6 +1779,12 @@
       <c r="G37" t="s">
         <v>68</v>
       </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1722,6 +1866,12 @@
       <c r="G40" t="s">
         <v>34</v>
       </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -1745,6 +1895,12 @@
       <c r="G41" t="s">
         <v>36</v>
       </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -1768,6 +1924,12 @@
       <c r="G42" t="s">
         <v>37</v>
       </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1791,6 +1953,12 @@
       <c r="G43" t="s">
         <v>36</v>
       </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1872,6 +2040,12 @@
       <c r="G46" t="s">
         <v>21</v>
       </c>
+      <c r="H46">
+        <v>2</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1895,6 +2069,12 @@
       <c r="G47" t="s">
         <v>47</v>
       </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1918,8 +2098,14 @@
       <c r="G48" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -1941,8 +2127,14 @@
       <c r="G49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>90</v>
       </c>
@@ -1964,8 +2156,14 @@
       <c r="G50" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -1987,8 +2185,14 @@
       <c r="G51" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -2010,8 +2214,14 @@
       <c r="G52" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <v>6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>90</v>
       </c>
@@ -2033,8 +2243,14 @@
       <c r="G53" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2056,8 +2272,14 @@
       <c r="G54" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2079,8 +2301,14 @@
       <c r="G55" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -2102,8 +2330,14 @@
       <c r="G56" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <v>3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -2125,8 +2359,14 @@
       <c r="G57" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -2148,8 +2388,14 @@
       <c r="G58" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <v>5</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -2171,8 +2417,14 @@
       <c r="G59" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -2194,8 +2446,14 @@
       <c r="G60" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -2217,8 +2475,14 @@
       <c r="G61" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2240,8 +2504,14 @@
       <c r="G62" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -2263,8 +2533,14 @@
       <c r="G63" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -2286,8 +2562,14 @@
       <c r="G64" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <v>2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>105</v>
       </c>
@@ -2309,8 +2591,14 @@
       <c r="G65" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <v>3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -2332,8 +2620,14 @@
       <c r="G66" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -2355,8 +2649,14 @@
       <c r="G67" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>111</v>
       </c>
@@ -2378,8 +2678,14 @@
       <c r="G68" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>111</v>
       </c>
@@ -2401,8 +2707,14 @@
       <c r="G69" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>111</v>
       </c>
@@ -2424,8 +2736,14 @@
       <c r="G70" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <v>3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>111</v>
       </c>
@@ -2447,8 +2765,14 @@
       <c r="G71" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>111</v>
       </c>
@@ -2470,8 +2794,14 @@
       <c r="G72" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>111</v>
       </c>
@@ -2492,6 +2822,12 @@
       </c>
       <c r="G73" t="s">
         <v>41</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
